--- a/Statistics/800m Fri_statistics.xlsx
+++ b/Statistics/800m Fri_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,12 +1101,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Joakim I. Larsen</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9.18,54</t>
+          <t>9.18,44</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.05.2008</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1136,12 +1136,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Joakim I. Larsen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9.18,53</t>
+          <t>9.18,54</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>25.05.2008</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9.18,44</t>
+          <t>9.18,53</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>15.01.2023</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1701,15 +1701,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9.58,59</t>
+          <t>9.55,33</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1841,15 +1841,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.53,52</t>
+          <t>10.50,71</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ole Andreas Alsos</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.04,66</t>
+          <t>10.04,57</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1976,12 +1976,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Ole Andreas Alsos</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.04,57</t>
+          <t>10.04,66</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2431,25 +2431,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10.49,07</t>
+          <t>10.48,50</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,25 +2466,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10.52,24</t>
+          <t>10.49,07</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2536,25 +2536,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10.55,66</t>
+          <t>10.52,24</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2571,25 +2571,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>11.05,81</t>
+          <t>10.55,66</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2781,25 +2781,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11.23,92</t>
+          <t>12.20,16</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>08.03.2019</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2816,25 +2816,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11.25,39</t>
+          <t>11.23,92</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>08.03.2019</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2851,20 +2851,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Christian Bauer</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11.26,24</t>
+          <t>11.25,39</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01.04.2011</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2886,25 +2886,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Christian Bauer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11.37,79</t>
+          <t>11.26,24</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>01.04.2011</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2921,20 +2921,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11.39,95</t>
+          <t>11.37,79</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2956,16 +2956,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11.40,57</t>
+          <t>11.39,95</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2991,20 +2991,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11.43,20</t>
+          <t>11.40,57</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3026,25 +3026,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11.44,69</t>
+          <t>11.43,20</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3061,25 +3061,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Geir Atle Hoff</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11.46,50</t>
+          <t>11.44,69</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>09.03.2012</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3096,25 +3096,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Geir Atle Hoff</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11.52,62</t>
+          <t>11.46,50</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>09.03.2012</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3131,25 +3131,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11.55,27</t>
+          <t>11.52,62</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3166,25 +3166,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11.58,49</t>
+          <t>11.55,27</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3201,20 +3201,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>11.59,90</t>
+          <t>11.58,49</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3271,20 +3271,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12.02,28</t>
+          <t>11.59,90</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3306,20 +3306,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12.07,72</t>
+          <t>13.01,51</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3341,20 +3341,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12.11,24</t>
+          <t>12.02,28</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3376,25 +3376,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Elias Hauge Lien</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12.16,14</t>
+          <t>12.07,72</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3411,20 +3411,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12.24,19</t>
+          <t>12.11,24</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3446,25 +3446,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Elias Hauge Lien</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12.25,25</t>
+          <t>12.16,14</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3481,20 +3481,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13.33,07</t>
+          <t>13.20,37</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3516,20 +3516,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Morten Schanke</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12.56,81</t>
+          <t>12.24,19</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3551,20 +3551,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14.10,88</t>
+          <t>12.25,25</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3586,20 +3586,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Håkon Emil Øien</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13.37,98</t>
+          <t>13.48,71</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3621,20 +3621,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14.09,81</t>
+          <t>12.47,81</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3656,25 +3656,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14.40,18</t>
+          <t>12.56,81</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3691,20 +3691,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fredrik Hårsaker Myrenget</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16.03,44</t>
+          <t>13.02,73</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13.09.2015</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3726,33 +3726,208 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>Håkon Emil Øien</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>13.37,98</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>156</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>16.09.2012</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tymofii Dzisiak</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>13.46,06</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>151</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>18.10.2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Vegard S. Wigum</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>14.09,81</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>139</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>16.09.2012</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Fredrik Hårsaker Myrenget</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>16.03,44</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>95</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>13.09.2015</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>Nataniel Skjøndal-Bar</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>16.11,34</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="C99" t="n">
         <v>93</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>20.10.2019</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Verdal</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guy Løfaldli</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>16.16,02</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>91</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>13.09.2025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4582,12 +4757,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11.24,15</t>
+          <t>11.24,39</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4595,7 +4770,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>18.04.2015</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4617,12 +4792,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11.24,39</t>
+          <t>11.24,15</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4630,7 +4805,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18.04.2015</t>
+          <t>26.04.2008</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4730,7 +4905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5998,25 +6173,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11.01,80</t>
+          <t>11.01,26</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6033,25 +6208,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rebekka Wangberg</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11.02,38</t>
+          <t>11.01,80</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31.10.2016</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6068,25 +6243,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Rebekka Wangberg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11.03,57</t>
+          <t>11.02,38</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13.03.2011</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6103,25 +6278,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.16,87</t>
+          <t>11.03,57</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>13.03.2011</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6138,25 +6313,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11.08,95</t>
+          <t>10.16,87</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6173,20 +6348,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11.10,57</t>
+          <t>11.08,95</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6208,20 +6383,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11.11,16</t>
+          <t>11.10,57</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31.10.2016</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6243,20 +6418,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Julie Mathilde Bjordal</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11.21,45</t>
+          <t>11.11,16</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6278,12 +6453,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Julie Mathilde Bjordal</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11.21,39</t>
+          <t>11.21,45</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -6291,7 +6466,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6313,25 +6488,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11.22,52</t>
+          <t>11.21,39</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6348,25 +6523,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11.22,82</t>
+          <t>11.22,52</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6383,25 +6558,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11.24,53</t>
+          <t>11.22,82</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6418,25 +6593,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11.28,64</t>
+          <t>11.24,53</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6453,20 +6628,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11.29,23</t>
+          <t>11.28,64</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6488,20 +6663,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ane Viken Refseth</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11.29,75</t>
+          <t>11.29,23</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13.09.2015</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6523,20 +6698,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Ane Viken Refseth</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11.30,29</t>
+          <t>11.29,75</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>13.09.2015</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6558,20 +6733,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11.33,85</t>
+          <t>11.30,29</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>01.11.2014</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6593,25 +6768,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Amanda Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11.40,41</t>
+          <t>11.33,85</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>01.11.2014</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6628,20 +6803,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Stine Tveit</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11.47,35</t>
+          <t>11.35,89</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6663,25 +6838,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Radana Konarikova</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11.48,24</t>
+          <t>11.40,41</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6698,20 +6873,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Stine Tveit</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11.50,93</t>
+          <t>11.47,35</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6733,20 +6908,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Radana Konarikova</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11.52,23</t>
+          <t>11.48,24</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6768,16 +6943,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11.55,26</t>
+          <t>11.52,23</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6803,25 +6978,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12.00,07</t>
+          <t>11.55,26</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6838,25 +7013,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12.07,13</t>
+          <t>11.58,13</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6873,25 +7048,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marte Hemmer</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12.13,81</t>
+          <t>12.00,07</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6908,20 +7083,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11.19,29</t>
+          <t>12.03,27</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6943,20 +7118,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12.23,39</t>
+          <t>12.07,13</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6978,20 +7153,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12.24,23</t>
+          <t>12.13,26</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7013,25 +7188,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Marte Hemmer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12.30,17</t>
+          <t>12.13,81</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7048,20 +7223,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hege Noreng</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12.34,62</t>
+          <t>11.19,29</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7083,20 +7258,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12.33,99</t>
+          <t>12.23,39</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7118,25 +7293,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12.36,41</t>
+          <t>12.24,23</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7153,25 +7328,25 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12.37,31</t>
+          <t>12.33,99</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7188,20 +7363,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Hege Noreng</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12.43,30</t>
+          <t>12.34,62</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7223,16 +7398,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12.45,62</t>
+          <t>12.36,41</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7258,25 +7433,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12.48,11</t>
+          <t>12.37,31</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7293,25 +7468,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12.50,44</t>
+          <t>12.43,30</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>28.03.2014</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7328,20 +7503,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12.52,11</t>
+          <t>12.48,11</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7363,25 +7538,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karoline Borg Simonsen</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12.55,42</t>
+          <t>12.50,44</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20.10.2018</t>
+          <t>28.03.2014</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7398,20 +7573,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aurora Moen Wannebo</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>13.01,67</t>
+          <t>12.52,11</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7433,25 +7608,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Karoline Borg Simonsen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13.53,42</t>
+          <t>12.55,42</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>20.10.2018</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7468,16 +7643,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Aurora Moen Wannebo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14.23,20</t>
+          <t>13.01,67</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7503,33 +7678,243 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>Elina Arefjord Spangelo</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>13.05,60</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>224</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>18.10.2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Louise Thys</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>13.49,32</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>190</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>13.09.2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Amalie Gylseth Dahl</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>13.53,42</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>187</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>09.11.2024</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aase Bjørnsdatter Paulsen</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>14.23,20</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>169</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>16.09.2012</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>Marie Wærnes Blom</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>14.41,88</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C84" t="n">
         <v>158</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>15.02.2025</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Kolvereid</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ilaria Kari Cherubini</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>14.52,31</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>153</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>18.10.2025</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oda Brennhaug Tangen</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>15.11,97</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>143</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>13.09.2025</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -7834,12 +8219,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.16,05</t>
+          <t>10.15,78</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -7847,12 +8232,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04.03.2011</t>
+          <t>28.04.2018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7869,12 +8254,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.15,78</t>
+          <t>10.16,05</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -7882,12 +8267,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.04.2018</t>
+          <t>04.03.2011</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">

--- a/Statistics/800m Fri_statistics.xlsx
+++ b/Statistics/800m Fri_statistics.xlsx
@@ -1101,12 +1101,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Joakim I. Larsen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9.18,44</t>
+          <t>9.18,54</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>25.05.2008</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1136,12 +1136,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Joakim I. Larsen</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9.18,54</t>
+          <t>9.18,53</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.05.2008</t>
+          <t>15.01.2023</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gabriel Rognes Steen</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9.18,53</t>
+          <t>9.18,44</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1486,25 +1486,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9.43,26</t>
+          <t>9.42,95</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>07.01.2018</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1521,25 +1521,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9.45,46</t>
+          <t>9.43,26</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>01.11.2014</t>
+          <t>07.01.2018</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1556,20 +1556,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ådne Viken Refseth</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9.49,29</t>
+          <t>9.45,46</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>01.11.2014</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Ådne Viken Refseth</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.38,86</t>
+          <t>9.49,29</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31.10.2016</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1626,20 +1626,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9.51,25</t>
+          <t>10.38,86</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1661,20 +1661,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maxim Sergeevich Gorodkov</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9.53,22</t>
+          <t>9.51,25</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1696,20 +1696,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Maxim Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9.55,33</t>
+          <t>9.53,22</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1836,20 +1836,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Margaret Kjøraas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.50,71</t>
+          <t>10.53,48</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1871,20 +1871,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Margaret Kjøraas</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10.53,48</t>
+          <t>10.03,83</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1906,20 +1906,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.03,83</t>
+          <t>10.04,57</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Ole Andreas Alsos</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.04,57</t>
+          <t>10.04,66</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1976,25 +1976,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ole Andreas Alsos</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.04,66</t>
+          <t>10.06,71</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2046,25 +2046,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10.06,71</t>
+          <t>10.07,94</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>30.09.2023</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2081,20 +2081,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10.07,94</t>
+          <t>10.14,55</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30.09.2023</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2116,25 +2116,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10.14,55</t>
+          <t>10.17,86</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>21.10.2022</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2151,25 +2151,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10.17,86</t>
+          <t>10.18,91</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21.10.2022</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2186,20 +2186,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Erin Elizabeth Bachynski</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10.18,91</t>
+          <t>11.11,15</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2221,25 +2221,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Erin Elizabeth Bachynski</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11.11,15</t>
+          <t>10.24,57</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2256,25 +2256,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10.24,57</t>
+          <t>10.32,29</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>21.10.2023</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2291,25 +2291,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Thais Farias Kristiansen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10.32,29</t>
+          <t>11.31,10</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21.10.2023</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2326,25 +2326,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Thais Farias Kristiansen</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11.31,10</t>
+          <t>10.41,43</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.41,43</t>
+          <t>10.41,77</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>21.04.2018</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2396,25 +2396,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10.41,77</t>
+          <t>10.48,50</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>21.04.2018</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2431,25 +2431,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10.48,50</t>
+          <t>10.49,07</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,20 +2466,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Edvin Aurstad Bergum</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10.49,07</t>
+          <t>10.52,63</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2501,12 +2501,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Edvin Aurstad Bergum</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10.52,63</t>
+          <t>10.52,24</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2536,25 +2536,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10.52,24</t>
+          <t>10.55,66</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2571,25 +2571,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Wiggo Røst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10.55,66</t>
+          <t>11.09,17</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>13.03.2009</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kirkenes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2606,25 +2606,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wiggo Røst</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>11.09,17</t>
+          <t>11.09,38</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2641,20 +2641,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>11.09,38</t>
+          <t>11.13,17</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2676,25 +2676,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>11.13,17</t>
+          <t>12.16,41</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2711,25 +2711,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12.16,41</t>
+          <t>11.21,55</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2746,25 +2746,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11.21,55</t>
+          <t>12.20,16</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2781,25 +2781,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12.20,16</t>
+          <t>11.23,92</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>08.03.2019</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2816,25 +2816,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11.23,92</t>
+          <t>11.25,39</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08.03.2019</t>
+          <t>27.10.2013</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2851,20 +2851,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Christian Bauer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11.25,39</t>
+          <t>11.26,24</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>27.10.2013</t>
+          <t>01.04.2011</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2886,25 +2886,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Christian Bauer</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11.26,24</t>
+          <t>11.37,79</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01.04.2011</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2921,20 +2921,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11.37,79</t>
+          <t>11.39,95</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2956,16 +2956,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11.39,95</t>
+          <t>11.40,57</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2991,20 +2991,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11.40,57</t>
+          <t>11.43,20</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3026,25 +3026,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>11.43,20</t>
+          <t>11.44,69</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3061,25 +3061,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Geir Atle Hoff</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>11.44,69</t>
+          <t>11.46,50</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>09.03.2012</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3096,25 +3096,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Geir Atle Hoff</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11.46,50</t>
+          <t>11.50,01</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09.03.2012</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3236,12 +3236,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11.59,63</t>
+          <t>11.59,90</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>09.03.2014</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11.59,90</t>
+          <t>11.59,63</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>09.03.2014</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3376,20 +3376,20 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12.07,72</t>
+          <t>12.05,42</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3411,20 +3411,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12.11,24</t>
+          <t>12.07,72</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3446,25 +3446,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Elias Hauge Lien</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12.16,14</t>
+          <t>12.11,24</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3481,25 +3481,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Elias Hauge Lien</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13.20,37</t>
+          <t>12.16,14</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3516,25 +3516,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12.24,19</t>
+          <t>13.20,37</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3551,20 +3551,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Morten Schanke</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12.25,25</t>
+          <t>12.24,19</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3586,20 +3586,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13.48,71</t>
+          <t>12.25,25</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3621,16 +3621,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12.47,81</t>
+          <t>13.48,71</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3656,20 +3656,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>12.56,81</t>
+          <t>12.47,81</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3691,20 +3691,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13.02,73</t>
+          <t>12.56,81</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4372,25 +4372,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.00,04</t>
+          <t>9.57,43</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19.06.2022</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4407,20 +4407,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.06,69</t>
+          <t>10.00,04</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.03.2021</t>
+          <t>19.06.2022</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4442,25 +4442,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.28,40</t>
+          <t>10.04,68</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>372</v>
+        <v>418</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>21.03.2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Oslo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4477,25 +4477,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.35,45</t>
+          <t>10.06,69</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.06.2014</t>
+          <t>13.03.2021</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4512,25 +4512,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.35,76</t>
+          <t>10.28,40</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.06.2022</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4547,16 +4547,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.36,27</t>
+          <t>10.35,45</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4582,25 +4582,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.39,30</t>
+          <t>10.36,27</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>13.03.2021</t>
+          <t>29.06.2014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4617,25 +4617,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.40,43</t>
+          <t>10.39,30</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21.04.2012</t>
+          <t>13.03.2021</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4652,16 +4652,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.57,75</t>
+          <t>10.40,43</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4687,20 +4687,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11.59,93</t>
+          <t>10.44,22</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.04.2016</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4722,20 +4722,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11.12,22</t>
+          <t>10.57,75</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>21.04.2012</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4757,20 +4757,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11.24,39</t>
+          <t>11.59,93</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18.04.2015</t>
+          <t>16.04.2016</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4792,20 +4792,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11.24,15</t>
+          <t>11.12,22</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4827,20 +4827,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Håkon Emil Øien</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12.55,95</t>
+          <t>11.21,42</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>197</v>
+        <v>292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4862,33 +4862,348 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Fredrik Holberg</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>11.23,01</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>290</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sondre Grimsmo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>11.24,15</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>288</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>26.04.2008</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Daniel Moen Manriquez</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>11.24,39</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>288</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>18.04.2015</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Olav Høyland Hofstad</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12.04,33</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>243</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ingeborg Strandenes</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>13.00,43</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>239</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Jesper Julius Sundseth Skjærli</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12.26,63</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>222</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Håkon Emil Øien</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>12.55,95</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>197</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>13.04.2013</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Tymofii Dzisiak</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>13.13,14</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>185</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mikkel Fenstad</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14.37,23</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>136</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Fredrik Hårsaker Myrenget</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>15.22,02</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C36" t="n">
         <v>117</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>16.04.2016</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Namsos</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>50m</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4905,7 +5220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5543,12 +5858,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.18,58</t>
+          <t>10.18,49</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5556,7 +5871,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5578,12 +5893,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marie Skuseth</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.18,49</t>
+          <t>10.18,58</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5591,7 +5906,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6033,20 +6348,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.56,72</t>
+          <t>10.50,71</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6068,20 +6383,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ingrid Vie</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.58,11</t>
+          <t>10.03,73</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6103,20 +6418,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Elisaveta Røste</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.58,27</t>
+          <t>10.56,72</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6138,20 +6453,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Ingrid Vie</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11.00,20</t>
+          <t>10.58,11</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6173,20 +6488,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Elisaveta Røste</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11.01,26</t>
+          <t>10.58,27</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6208,25 +6523,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11.01,80</t>
+          <t>11.00,20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6243,20 +6558,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rebekka Wangberg</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11.02,38</t>
+          <t>11.01,26</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31.10.2016</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6278,25 +6593,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11.03,57</t>
+          <t>11.01,80</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.03.2011</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6313,25 +6628,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Rebekka Wangberg</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.16,87</t>
+          <t>11.02,38</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6348,25 +6663,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11.08,95</t>
+          <t>11.03,57</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>13.03.2011</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6383,20 +6698,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11.10,57</t>
+          <t>11.08,95</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6418,20 +6733,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11.11,16</t>
+          <t>11.10,57</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>31.10.2016</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6453,20 +6768,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Julie Mathilde Bjordal</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>11.21,45</t>
+          <t>11.11,16</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>31.10.2016</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6488,12 +6803,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Julie Mathilde Bjordal</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11.21,39</t>
+          <t>11.21,45</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -6501,7 +6816,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6523,25 +6838,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11.22,52</t>
+          <t>11.21,39</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6558,25 +6873,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11.22,82</t>
+          <t>11.22,52</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6593,25 +6908,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11.24,53</t>
+          <t>11.22,82</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6628,25 +6943,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11.28,64</t>
+          <t>11.24,53</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6663,20 +6978,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11.29,23</t>
+          <t>11.28,64</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6698,20 +7013,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ane Viken Refseth</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11.29,75</t>
+          <t>11.29,23</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>13.09.2015</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6733,20 +7048,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Ane Viken Refseth</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11.30,29</t>
+          <t>11.29,75</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>13.09.2015</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6768,20 +7083,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11.33,85</t>
+          <t>11.30,29</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>01.11.2014</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6803,20 +7118,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Amanda Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11.35,89</t>
+          <t>11.33,85</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>01.11.2014</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6838,25 +7153,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11.40,41</t>
+          <t>11.35,89</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6873,25 +7188,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Stine Tveit</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11.47,35</t>
+          <t>11.40,41</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6908,20 +7223,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Radana Konarikova</t>
+          <t>Stine Tveit</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11.48,24</t>
+          <t>11.47,35</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6943,20 +7258,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Radana Konarikova</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11.52,23</t>
+          <t>11.48,24</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6978,16 +7293,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11.55,26</t>
+          <t>11.52,23</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7013,25 +7328,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>11.58,13</t>
+          <t>11.55,26</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7048,25 +7363,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12.00,07</t>
+          <t>11.58,13</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15.10.2011</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7083,25 +7398,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12.03,27</t>
+          <t>12.00,07</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>15.10.2011</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7118,20 +7433,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12.07,13</t>
+          <t>12.03,27</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7153,20 +7468,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sofie Hepsø</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>12.13,26</t>
+          <t>12.07,13</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7188,20 +7503,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marte Hemmer</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12.13,81</t>
+          <t>12.13,26</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7223,20 +7538,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Marte Hemmer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11.19,29</t>
+          <t>12.13,81</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7258,20 +7573,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12.23,39</t>
+          <t>11.19,29</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7293,16 +7608,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12.24,23</t>
+          <t>12.23,39</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7328,20 +7643,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12.33,99</t>
+          <t>12.24,46</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>24.01.2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7363,20 +7678,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hege Noreng</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12.34,62</t>
+          <t>12.24,23</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>08.04.2016</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7398,25 +7713,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12.36,41</t>
+          <t>12.32,19</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>24.01.2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7433,25 +7748,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Hege Noreng</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12.37,31</t>
+          <t>12.34,62</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>08.04.2016</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7468,20 +7783,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12.43,30</t>
+          <t>12.33,99</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7503,25 +7818,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12.48,11</t>
+          <t>12.36,41</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7538,25 +7853,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12.50,44</t>
+          <t>12.37,31</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>28.03.2014</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7573,20 +7888,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12.52,11</t>
+          <t>12.43,30</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7608,25 +7923,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Karoline Borg Simonsen</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12.55,42</t>
+          <t>12.48,11</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20.10.2018</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7643,25 +7958,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aurora Moen Wannebo</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13.01,67</t>
+          <t>12.50,44</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>28.03.2014</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7678,25 +7993,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13.05,60</t>
+          <t>12.52,11</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7713,25 +8028,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Karoline Borg Simonsen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13.49,32</t>
+          <t>12.55,42</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>13.09.2025</t>
+          <t>20.10.2018</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7748,20 +8063,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Aurora Moen Wannebo</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13.53,42</t>
+          <t>13.01,67</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7783,25 +8098,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14.23,20</t>
+          <t>13.05,60</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>16.09.2012</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7818,25 +8133,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Amalie Gylseth Dahl</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>14.41,88</t>
+          <t>13.53,42</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7853,25 +8168,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ilaria Kari Cherubini</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>14.52,31</t>
+          <t>14.23,20</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>18.10.2025</t>
+          <t>16.09.2012</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7888,33 +8203,68 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>Ilaria Kari Cherubini</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>14.52,31</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>153</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>18.10.2025</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>Oda Brennhaug Tangen</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>15.11,97</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C87" t="n">
         <v>143</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>13.09.2025</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -7931,7 +8281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8219,12 +8569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.15,78</t>
+          <t>10.16,05</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -8232,12 +8582,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>28.04.2018</t>
+          <t>04.03.2011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8254,12 +8604,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.16,05</t>
+          <t>10.15,78</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8267,12 +8617,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04.03.2011</t>
+          <t>28.04.2018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -8464,25 +8814,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11.09,57</t>
+          <t>11.03,08</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.04.2006</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8499,20 +8849,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11.10,94</t>
+          <t>11.09,57</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>29.04.2006</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8534,20 +8884,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11.17,05</t>
+          <t>11.10,94</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>26.04.2008</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8569,20 +8919,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11.22,28</t>
+          <t>11.17,05</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.04.2015</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8604,20 +8954,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ingrid Elverum</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11.33,61</t>
+          <t>11.22,28</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>19.04.2015</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8639,25 +8989,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Ingrid Elverum</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11.45,87</t>
+          <t>11.33,61</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>29.08.2015</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -8674,25 +9024,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Andrea Lintorp</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12.18,07</t>
+          <t>11.45,87</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>09.04.2011</t>
+          <t>29.08.2015</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8709,25 +9059,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12.25,61</t>
+          <t>12.08,15</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13.03.2021</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8744,20 +9094,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Live Killingberg Sandberg</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12.28,08</t>
+          <t>12.08,09</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30.03.2019</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8779,20 +9129,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Andrea Lintorp</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12.34,14</t>
+          <t>12.18,07</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21.04.2012</t>
+          <t>09.04.2011</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -8814,20 +9164,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13.25,69</t>
+          <t>12.23,55</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>217</v>
+        <v>277</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>26.04.2014</t>
+          <t>25.04.2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8849,33 +9199,348 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Thora Bjarnøe Brandsegg</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12.25,61</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>274</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>13.03.2021</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Live Killingberg Sandberg</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12.28,08</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>272</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>30.03.2019</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thea Lervold Høffler</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>12.34,14</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>265</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>21.04.2012</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Marie Wærnes Blom</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12.41,68</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>257</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ina Birgitte Eidsmo Hova</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>12.47,20</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>252</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ilaria Kari Cherubini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13.17,24</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>224</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hedda Fosseng Traa</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>13.25,69</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>217</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>26.04.2014</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Hilde Stene Rygh</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>13.31,61</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C34" t="n">
         <v>213</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>25.10.2019</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Vantaa</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>50m</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sigrid Gylseth Dahl</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14.08,80</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>186</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>25.04.2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Aurora Aarflot Johannessen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15.47,99</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>133</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>06.06.2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
